--- a/uploads/import_files/Time and Attendance.xlsx
+++ b/uploads/import_files/Time and Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Modular1\uploads\import_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA35C679-B2F2-40F2-B80E-3B3562653FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8BB3F1-53FA-46CF-B1F5-F6BAFEB100C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,110 +89,116 @@
     <t>Vortsman</t>
   </si>
   <si>
-    <t>EMP1005</t>
-  </si>
-  <si>
-    <t>EMP1001</t>
-  </si>
-  <si>
     <t>John</t>
   </si>
   <si>
     <t>Doe</t>
   </si>
   <si>
-    <t>EMP1002</t>
-  </si>
-  <si>
     <t>Jane</t>
   </si>
   <si>
     <t>Smith</t>
   </si>
   <si>
-    <t>EMP1003</t>
-  </si>
-  <si>
     <t>Michael</t>
   </si>
   <si>
     <t>Jones</t>
   </si>
   <si>
-    <t>EMP1004</t>
-  </si>
-  <si>
     <t>Robert</t>
   </si>
   <si>
     <t>Lee</t>
   </si>
   <si>
-    <t>EMP1006</t>
-  </si>
-  <si>
     <t>Sarah</t>
   </si>
   <si>
     <t>Johnson</t>
   </si>
   <si>
-    <t>EMP1007</t>
-  </si>
-  <si>
     <t>David</t>
   </si>
   <si>
     <t>Williams</t>
   </si>
   <si>
-    <t>EMP1008</t>
-  </si>
-  <si>
     <t>Linda</t>
   </si>
   <si>
     <t>Brown</t>
   </si>
   <si>
-    <t>EMP1009</t>
-  </si>
-  <si>
     <t>James</t>
   </si>
   <si>
     <t>Miller</t>
   </si>
   <si>
-    <t>EMP1010</t>
-  </si>
-  <si>
     <t>Olivia</t>
   </si>
   <si>
     <t>Moore</t>
   </si>
   <si>
-    <t>EMP1011</t>
-  </si>
-  <si>
     <t>William</t>
   </si>
   <si>
     <t>Wilson</t>
   </si>
   <si>
-    <t>EMP1012</t>
+    <t>EMP2001</t>
+  </si>
+  <si>
+    <t>EMP2002</t>
+  </si>
+  <si>
+    <t>EMP2003</t>
+  </si>
+  <si>
+    <t>EMP2004</t>
+  </si>
+  <si>
+    <t>EMP2005</t>
+  </si>
+  <si>
+    <t>EMP2006</t>
+  </si>
+  <si>
+    <t>EMP2007</t>
+  </si>
+  <si>
+    <t>EMP2008</t>
+  </si>
+  <si>
+    <t>EMP2009</t>
+  </si>
+  <si>
+    <t>EMP2010</t>
+  </si>
+  <si>
+    <t>EMP2011</t>
+  </si>
+  <si>
+    <t>EMP2012</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -634,10 +640,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D2">
-        <v>1005</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -648,153 +654,154 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D3">
-        <v>1001</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D4">
-        <v>1002</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D5">
-        <v>1003</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D6">
-        <v>1004</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D7">
-        <v>1006</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D8">
-        <v>1007</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D9">
-        <v>1008</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D10">
-        <v>1009</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D11">
-        <v>1010</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12">
-        <v>1011</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
         <v>52</v>
       </c>
       <c r="D13">
-        <v>1012</v>
+        <v>2012</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
